--- a/backtest_runs/20260410_193731/by_symbol/SKRS/SKRS.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/SKRS/SKRS.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
         <v>-434.9699999999993</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" s="3" t="n">
         <v>102223.18</v>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>102223.18</v>
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>106331.23</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>106331.23</v>
@@ -909,7 +909,7 @@
         <v>-4591.350000000014</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>104736.34</v>
@@ -955,7 +955,7 @@
         <v>-1014.929999999987</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>103721.41</v>
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>103721.41</v>
@@ -1185,7 +1185,7 @@
         <v>-3238.109999999991</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>101546.56</v>
@@ -1231,7 +1231,7 @@
         <v>-48.33000000000756</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>101498.23</v>
@@ -1277,7 +1277,7 @@
         <v>-3044.789999999995</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>98453.44</v>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>98453.44</v>
@@ -1415,7 +1415,7 @@
         <v>-2029.859999999991</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>96423.58</v>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>96423.58</v>
